--- a/www/flightdata/xlsx/eoss-370.xlsx
+++ b/www/flightdata/xlsx/eoss-370.xlsx
@@ -4992,7 +4992,7 @@
         <v>28635.66</v>
       </c>
       <c r="I2">
-        <v>969</v>
+        <v>695</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
